--- a/src/test/resources/files/CommonMessages.xlsx
+++ b/src/test/resources/files/CommonMessages.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E472A7A8-ED52-4802-942E-2E2938A6260E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE19F9B-066C-490A-AFAC-4E0BC085BEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29940" yWindow="1140" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <t>commonError</t>
   </si>
   <si>
-    <t>Bad Request Data.</t>
+    <t>Bad Request Data</t>
   </si>
 </sst>
 </file>
